--- a/Hardware/BOM.xlsx
+++ b/Hardware/BOM.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E63D549-C818-45CB-8236-CD79E22B6E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAEE33E-95BB-48F3-9E88-041FBE12300F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Main" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="176">
   <si>
     <t>No.</t>
   </si>
@@ -537,6 +537,18 @@
   </si>
   <si>
     <t>https://e.tb.cn/h.iamBiH13oK2KlH0?tk=OH2pUqX8oit MF937</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锂电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Size:40x20x5(mm)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -935,13 +947,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -961,7 +973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -981,7 +993,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1001,7 +1013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1021,7 +1033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1041,7 +1053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1061,7 +1073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1081,7 +1093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1101,7 +1113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1121,7 +1133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1141,7 +1153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1161,7 +1173,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1181,7 +1193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1201,7 +1213,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -1241,7 +1253,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1261,7 +1273,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1281,7 +1293,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1301,7 +1313,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1321,7 +1333,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -1341,7 +1353,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -1361,7 +1373,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -1381,7 +1393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -1401,7 +1413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -1421,7 +1433,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>83</v>
       </c>
@@ -1441,7 +1453,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -1461,7 +1473,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>90</v>
       </c>
@@ -1481,7 +1493,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>97</v>
       </c>
@@ -1521,7 +1533,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>99</v>
       </c>
@@ -1541,7 +1553,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -1561,7 +1573,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -1581,7 +1593,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>108</v>
       </c>
@@ -1601,7 +1613,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -1621,7 +1633,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>113</v>
       </c>
@@ -1641,7 +1653,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -1661,7 +1673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -1681,7 +1693,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>124</v>
       </c>
@@ -1701,7 +1713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>128</v>
       </c>
@@ -1721,7 +1733,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -1741,7 +1753,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>136</v>
       </c>
@@ -1761,7 +1773,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>140</v>
       </c>
@@ -1781,7 +1793,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -1801,7 +1813,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>148</v>
       </c>
@@ -1821,7 +1833,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -1841,7 +1853,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>156</v>
       </c>
@@ -1861,7 +1873,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>160</v>
       </c>
@@ -1881,7 +1893,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1939,6 +1951,23 @@
       </c>
       <c r="F50" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
